--- a/StructureDefinition-swallowing-screening-result.xlsx
+++ b/StructureDefinition-swallowing-screening-result.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.1.0</t>
+    <t>1.0.1</t>
   </si>
   <si>
     <t>Name</t>
@@ -51,7 +51,7 @@
     <t>Status</t>
   </si>
   <si>
-    <t>draft</t>
+    <t>active</t>
   </si>
   <si>
     <t>Experimental</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-28T10:20:05+00:00</t>
+    <t>2026-07-28T10:50:36+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-swallowing-screening-result.xlsx
+++ b/StructureDefinition-swallowing-screening-result.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1993" uniqueCount="447">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1994" uniqueCount="448">
   <si>
     <t>Property</t>
   </si>
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.0.1</t>
+    <t>1.1.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-28T10:50:36+00:00</t>
+    <t>2026-07-29T08:35:16+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -85,6 +85,9 @@
   </si>
   <si>
     <t>Copyright</t>
+  </si>
+  <si>
+    <t>© 2026 N. Kapan Tunçer and S. Tunçer. IG artifacts licensed under the MIT License. This IG references but does not redistribute SNOMED CT (© SNOMED International), LOINC (© Regenstrief Institute, Inc.) and the IDDSI framework (CC BY-SA 4.0, used unmodified); value sets enumerate concept identifiers only, so display terms are supplied at expansion time by the implementer's own terminology server. Implementers are responsible for holding the applicable third-party licences.</t>
   </si>
   <si>
     <t>FHIR Version</t>
@@ -1666,54 +1669,56 @@
       <c r="A13" t="s" s="2">
         <v>22</v>
       </c>
-      <c r="B13" s="2"/>
+      <c r="B13" t="s" s="2">
+        <v>23</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="s" s="2">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B14" t="s" s="2">
-        <v>24</v>
+        <v>25</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="s" s="2">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="B15" t="s" s="2">
-        <v>26</v>
+        <v>27</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="s" s="2">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="B16" t="s" s="2">
-        <v>28</v>
+        <v>29</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="s" s="2">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B17" t="s" s="2">
-        <v>30</v>
+        <v>31</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="s" s="2">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="B18" t="s" s="2">
-        <v>32</v>
+        <v>33</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="s" s="2">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B19" t="s" s="2">
-        <v>34</v>
+        <v>35</v>
       </c>
     </row>
   </sheetData>
@@ -1771,149 +1776,149 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s" s="1">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="B1" t="s" s="1">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="C1" t="s" s="1">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="D1" t="s" s="1">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="E1" t="s" s="1">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="F1" t="s" s="1">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="G1" t="s" s="1">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="H1" t="s" s="1">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="I1" t="s" s="1">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="J1" t="s" s="1">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="K1" t="s" s="1">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="L1" t="s" s="1">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="M1" t="s" s="1">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="N1" t="s" s="1">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="O1" t="s" s="1">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="P1" t="s" s="1">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="Q1" t="s" s="1">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="R1" t="s" s="1">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="S1" t="s" s="1">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="T1" t="s" s="1">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="U1" t="s" s="1">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="V1" t="s" s="1">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="W1" t="s" s="1">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="X1" t="s" s="1">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="Y1" t="s" s="1">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="Z1" t="s" s="1">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="AA1" t="s" s="1">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="AB1" t="s" s="1">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="AC1" t="s" s="1">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="AD1" t="s" s="1">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="AE1" t="s" s="1">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="AF1" t="s" s="1">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="AG1" t="s" s="1">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="AH1" t="s" s="1">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="AI1" t="s" s="1">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="AJ1" t="s" s="1">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="AK1" t="s" s="1">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="AL1" t="s" s="1">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="AM1" t="s" s="1">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="AN1" t="s" s="1">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="AO1" t="s" s="1">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="AP1" t="s" s="1">
-        <v>76</v>
+        <v>77</v>
       </c>
     </row>
     <row r="2" hidden="true">
       <c r="A2" t="s" s="2">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="B2" t="s" s="2">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="C2" s="2"/>
       <c r="D2" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="E2" s="2"/>
       <c r="F2" t="s" s="2">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="G2" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="H2" t="s" s="2">
         <v>18</v>
@@ -1925,16 +1930,16 @@
         <v>18</v>
       </c>
       <c r="K2" t="s" s="2">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="L2" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="M2" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="N2" t="s" s="2">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="O2" s="2"/>
       <c r="P2" t="s" s="2">
@@ -1984,31 +1989,31 @@
         <v>18</v>
       </c>
       <c r="AF2" t="s" s="2">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="AG2" t="s" s="2">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="AH2" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AI2" t="s" s="2">
         <v>18</v>
       </c>
       <c r="AJ2" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AK2" t="s" s="2">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="AL2" t="s" s="2">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="AM2" t="s" s="2">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="AN2" t="s" s="2">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="AO2" t="s" s="2">
         <v>18</v>
@@ -2019,10 +2024,10 @@
     </row>
     <row r="3" hidden="true">
       <c r="A3" t="s" s="2">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="B3" t="s" s="2">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="C3" s="2"/>
       <c r="D3" t="s" s="2">
@@ -2030,10 +2035,10 @@
       </c>
       <c r="E3" s="2"/>
       <c r="F3" t="s" s="2">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="G3" t="s" s="2">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="H3" t="s" s="2">
         <v>18</v>
@@ -2042,19 +2047,19 @@
         <v>18</v>
       </c>
       <c r="J3" t="s" s="2">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="K3" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="L3" t="s" s="2">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="M3" t="s" s="2">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="N3" t="s" s="2">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="O3" s="2"/>
       <c r="P3" t="s" s="2">
@@ -2104,13 +2109,13 @@
         <v>18</v>
       </c>
       <c r="AF3" t="s" s="2">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="AG3" t="s" s="2">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="AH3" t="s" s="2">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="AI3" t="s" s="2">
         <v>18</v>
@@ -2139,10 +2144,10 @@
     </row>
     <row r="4" hidden="true">
       <c r="A4" t="s" s="2">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="B4" t="s" s="2">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="C4" s="2"/>
       <c r="D4" t="s" s="2">
@@ -2150,10 +2155,10 @@
       </c>
       <c r="E4" s="2"/>
       <c r="F4" t="s" s="2">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="G4" t="s" s="2">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="H4" t="s" s="2">
         <v>18</v>
@@ -2162,16 +2167,16 @@
         <v>18</v>
       </c>
       <c r="J4" t="s" s="2">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="K4" t="s" s="2">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="L4" t="s" s="2">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="M4" t="s" s="2">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="N4" s="2"/>
       <c r="O4" s="2"/>
@@ -2222,19 +2227,19 @@
         <v>18</v>
       </c>
       <c r="AF4" t="s" s="2">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="AG4" t="s" s="2">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="AH4" t="s" s="2">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="AI4" t="s" s="2">
         <v>18</v>
       </c>
       <c r="AJ4" t="s" s="2">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="AK4" t="s" s="2">
         <v>18</v>
@@ -2257,10 +2262,10 @@
     </row>
     <row r="5" hidden="true">
       <c r="A5" t="s" s="2">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="B5" t="s" s="2">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="C5" s="2"/>
       <c r="D5" t="s" s="2">
@@ -2268,31 +2273,31 @@
       </c>
       <c r="E5" s="2"/>
       <c r="F5" t="s" s="2">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="G5" t="s" s="2">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="H5" t="s" s="2">
         <v>18</v>
       </c>
       <c r="I5" t="s" s="2">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="J5" t="s" s="2">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="K5" t="s" s="2">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="L5" t="s" s="2">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="M5" t="s" s="2">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="N5" t="s" s="2">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="O5" s="2"/>
       <c r="P5" t="s" s="2">
@@ -2342,19 +2347,19 @@
         <v>18</v>
       </c>
       <c r="AF5" t="s" s="2">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="AG5" t="s" s="2">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="AH5" t="s" s="2">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="AI5" t="s" s="2">
         <v>18</v>
       </c>
       <c r="AJ5" t="s" s="2">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="AK5" t="s" s="2">
         <v>18</v>
@@ -2377,10 +2382,10 @@
     </row>
     <row r="6" hidden="true">
       <c r="A6" t="s" s="2">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="B6" t="s" s="2">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="C6" s="2"/>
       <c r="D6" t="s" s="2">
@@ -2388,10 +2393,10 @@
       </c>
       <c r="E6" s="2"/>
       <c r="F6" t="s" s="2">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="G6" t="s" s="2">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="H6" t="s" s="2">
         <v>18</v>
@@ -2403,16 +2408,16 @@
         <v>18</v>
       </c>
       <c r="K6" t="s" s="2">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="L6" t="s" s="2">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="M6" t="s" s="2">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="N6" t="s" s="2">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="O6" s="2"/>
       <c r="P6" t="s" s="2">
@@ -2438,13 +2443,13 @@
         <v>18</v>
       </c>
       <c r="X6" t="s" s="2">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="Y6" t="s" s="2">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="Z6" t="s" s="2">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="AA6" t="s" s="2">
         <v>18</v>
@@ -2462,19 +2467,19 @@
         <v>18</v>
       </c>
       <c r="AF6" t="s" s="2">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="AG6" t="s" s="2">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="AH6" t="s" s="2">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="AI6" t="s" s="2">
         <v>18</v>
       </c>
       <c r="AJ6" t="s" s="2">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="AK6" t="s" s="2">
         <v>18</v>
@@ -2497,21 +2502,21 @@
     </row>
     <row r="7" hidden="true">
       <c r="A7" t="s" s="2">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="B7" t="s" s="2">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="C7" s="2"/>
       <c r="D7" t="s" s="2">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="E7" s="2"/>
       <c r="F7" t="s" s="2">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="G7" t="s" s="2">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="H7" t="s" s="2">
         <v>18</v>
@@ -2523,16 +2528,16 @@
         <v>18</v>
       </c>
       <c r="K7" t="s" s="2">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="L7" t="s" s="2">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="M7" t="s" s="2">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="N7" t="s" s="2">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="O7" s="2"/>
       <c r="P7" t="s" s="2">
@@ -2582,19 +2587,19 @@
         <v>18</v>
       </c>
       <c r="AF7" t="s" s="2">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="AG7" t="s" s="2">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="AH7" t="s" s="2">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="AI7" t="s" s="2">
         <v>18</v>
       </c>
       <c r="AJ7" t="s" s="2">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="AK7" t="s" s="2">
         <v>18</v>
@@ -2606,7 +2611,7 @@
         <v>18</v>
       </c>
       <c r="AN7" t="s" s="2">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="AO7" t="s" s="2">
         <v>18</v>
@@ -2617,21 +2622,21 @@
     </row>
     <row r="8" hidden="true">
       <c r="A8" t="s" s="2">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="B8" t="s" s="2">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="C8" s="2"/>
       <c r="D8" t="s" s="2">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="E8" s="2"/>
       <c r="F8" t="s" s="2">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="G8" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="H8" t="s" s="2">
         <v>18</v>
@@ -2643,16 +2648,16 @@
         <v>18</v>
       </c>
       <c r="K8" t="s" s="2">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="L8" t="s" s="2">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="M8" t="s" s="2">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="N8" t="s" s="2">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="O8" s="2"/>
       <c r="P8" t="s" s="2">
@@ -2702,13 +2707,13 @@
         <v>18</v>
       </c>
       <c r="AF8" t="s" s="2">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="AG8" t="s" s="2">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="AH8" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AI8" t="s" s="2">
         <v>18</v>
@@ -2726,7 +2731,7 @@
         <v>18</v>
       </c>
       <c r="AN8" t="s" s="2">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="AO8" t="s" s="2">
         <v>18</v>
@@ -2737,21 +2742,21 @@
     </row>
     <row r="9" hidden="true">
       <c r="A9" t="s" s="2">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="B9" t="s" s="2">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="C9" s="2"/>
       <c r="D9" t="s" s="2">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="E9" s="2"/>
       <c r="F9" t="s" s="2">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="G9" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="H9" t="s" s="2">
         <v>18</v>
@@ -2763,16 +2768,16 @@
         <v>18</v>
       </c>
       <c r="K9" t="s" s="2">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="L9" t="s" s="2">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="M9" t="s" s="2">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="N9" t="s" s="2">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="O9" s="2"/>
       <c r="P9" t="s" s="2">
@@ -2822,19 +2827,19 @@
         <v>18</v>
       </c>
       <c r="AF9" t="s" s="2">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="AG9" t="s" s="2">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="AH9" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AI9" t="s" s="2">
         <v>18</v>
       </c>
       <c r="AJ9" t="s" s="2">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="AK9" t="s" s="2">
         <v>18</v>
@@ -2846,7 +2851,7 @@
         <v>18</v>
       </c>
       <c r="AN9" t="s" s="2">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="AO9" t="s" s="2">
         <v>18</v>
@@ -2857,45 +2862,45 @@
     </row>
     <row r="10" hidden="true">
       <c r="A10" t="s" s="2">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="B10" t="s" s="2">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="C10" s="2"/>
       <c r="D10" t="s" s="2">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="E10" s="2"/>
       <c r="F10" t="s" s="2">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="G10" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="H10" t="s" s="2">
         <v>18</v>
       </c>
       <c r="I10" t="s" s="2">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="J10" t="s" s="2">
         <v>18</v>
       </c>
       <c r="K10" t="s" s="2">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="L10" t="s" s="2">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="M10" t="s" s="2">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="N10" t="s" s="2">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="O10" t="s" s="2">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="P10" t="s" s="2">
         <v>18</v>
@@ -2944,19 +2949,19 @@
         <v>18</v>
       </c>
       <c r="AF10" t="s" s="2">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="AG10" t="s" s="2">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="AH10" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AI10" t="s" s="2">
         <v>18</v>
       </c>
       <c r="AJ10" t="s" s="2">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="AK10" t="s" s="2">
         <v>18</v>
@@ -2968,7 +2973,7 @@
         <v>18</v>
       </c>
       <c r="AN10" t="s" s="2">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="AO10" t="s" s="2">
         <v>18</v>
@@ -2979,10 +2984,10 @@
     </row>
     <row r="11" hidden="true">
       <c r="A11" t="s" s="2">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="B11" t="s" s="2">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="C11" s="2"/>
       <c r="D11" t="s" s="2">
@@ -2990,10 +2995,10 @@
       </c>
       <c r="E11" s="2"/>
       <c r="F11" t="s" s="2">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="G11" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="H11" t="s" s="2">
         <v>18</v>
@@ -3002,20 +3007,20 @@
         <v>18</v>
       </c>
       <c r="J11" t="s" s="2">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="K11" t="s" s="2">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="L11" t="s" s="2">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="M11" t="s" s="2">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="N11" s="2"/>
       <c r="O11" t="s" s="2">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="P11" t="s" s="2">
         <v>18</v>
@@ -3064,34 +3069,34 @@
         <v>18</v>
       </c>
       <c r="AF11" t="s" s="2">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="AG11" t="s" s="2">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="AH11" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AI11" t="s" s="2">
         <v>18</v>
       </c>
       <c r="AJ11" t="s" s="2">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="AK11" t="s" s="2">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="AL11" t="s" s="2">
         <v>18</v>
       </c>
       <c r="AM11" t="s" s="2">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="AN11" t="s" s="2">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="AO11" t="s" s="2">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="AP11" t="s" s="2">
         <v>18</v>
@@ -3099,21 +3104,21 @@
     </row>
     <row r="12" hidden="true">
       <c r="A12" t="s" s="2">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="B12" t="s" s="2">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="C12" s="2"/>
       <c r="D12" t="s" s="2">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="E12" s="2"/>
       <c r="F12" t="s" s="2">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="G12" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="H12" t="s" s="2">
         <v>18</v>
@@ -3122,20 +3127,20 @@
         <v>18</v>
       </c>
       <c r="J12" t="s" s="2">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="K12" t="s" s="2">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="L12" t="s" s="2">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="M12" t="s" s="2">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="N12" s="2"/>
       <c r="O12" t="s" s="2">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="P12" t="s" s="2">
         <v>18</v>
@@ -3184,31 +3189,31 @@
         <v>18</v>
       </c>
       <c r="AF12" t="s" s="2">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="AG12" t="s" s="2">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="AH12" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AI12" t="s" s="2">
         <v>18</v>
       </c>
       <c r="AJ12" t="s" s="2">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="AK12" t="s" s="2">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="AL12" t="s" s="2">
         <v>18</v>
       </c>
       <c r="AM12" t="s" s="2">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="AN12" t="s" s="2">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="AO12" t="s" s="2">
         <v>18</v>
@@ -3219,21 +3224,21 @@
     </row>
     <row r="13" hidden="true">
       <c r="A13" t="s" s="2">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="B13" t="s" s="2">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="C13" s="2"/>
       <c r="D13" t="s" s="2">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="E13" s="2"/>
       <c r="F13" t="s" s="2">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="G13" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="H13" t="s" s="2">
         <v>18</v>
@@ -3242,19 +3247,19 @@
         <v>18</v>
       </c>
       <c r="J13" t="s" s="2">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="K13" t="s" s="2">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="L13" t="s" s="2">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="M13" t="s" s="2">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="N13" t="s" s="2">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="O13" s="2"/>
       <c r="P13" t="s" s="2">
@@ -3304,31 +3309,31 @@
         <v>18</v>
       </c>
       <c r="AF13" t="s" s="2">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="AG13" t="s" s="2">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="AH13" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AI13" t="s" s="2">
         <v>18</v>
       </c>
       <c r="AJ13" t="s" s="2">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="AK13" t="s" s="2">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="AL13" t="s" s="2">
         <v>18</v>
       </c>
       <c r="AM13" t="s" s="2">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="AN13" t="s" s="2">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="AO13" t="s" s="2">
         <v>18</v>
@@ -3339,10 +3344,10 @@
     </row>
     <row r="14">
       <c r="A14" t="s" s="2">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="B14" t="s" s="2">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="C14" s="2"/>
       <c r="D14" t="s" s="2">
@@ -3350,41 +3355,41 @@
       </c>
       <c r="E14" s="2"/>
       <c r="F14" t="s" s="2">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="G14" t="s" s="2">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="H14" t="s" s="2">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="I14" t="s" s="2">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="J14" t="s" s="2">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="K14" t="s" s="2">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="L14" t="s" s="2">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="M14" t="s" s="2">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="N14" t="s" s="2">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="O14" t="s" s="2">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="P14" t="s" s="2">
         <v>18</v>
       </c>
       <c r="Q14" s="2"/>
       <c r="R14" t="s" s="2">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="S14" t="s" s="2">
         <v>18</v>
@@ -3402,13 +3407,13 @@
         <v>18</v>
       </c>
       <c r="X14" t="s" s="2">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="Y14" t="s" s="2">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="Z14" t="s" s="2">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="AA14" t="s" s="2">
         <v>18</v>
@@ -3426,34 +3431,34 @@
         <v>18</v>
       </c>
       <c r="AF14" t="s" s="2">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="AG14" t="s" s="2">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="AH14" t="s" s="2">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="AI14" t="s" s="2">
         <v>18</v>
       </c>
       <c r="AJ14" t="s" s="2">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="AK14" t="s" s="2">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="AL14" t="s" s="2">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="AM14" t="s" s="2">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="AN14" t="s" s="2">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="AO14" t="s" s="2">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="AP14" t="s" s="2">
         <v>18</v>
@@ -3461,10 +3466,10 @@
     </row>
     <row r="15" hidden="true">
       <c r="A15" t="s" s="2">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="B15" t="s" s="2">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="C15" s="2"/>
       <c r="D15" t="s" s="2">
@@ -3472,10 +3477,10 @@
       </c>
       <c r="E15" s="2"/>
       <c r="F15" t="s" s="2">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="G15" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="H15" t="s" s="2">
         <v>18</v>
@@ -3487,19 +3492,19 @@
         <v>18</v>
       </c>
       <c r="K15" t="s" s="2">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="L15" t="s" s="2">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="M15" t="s" s="2">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="N15" t="s" s="2">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="O15" t="s" s="2">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="P15" t="s" s="2">
         <v>18</v>
@@ -3524,13 +3529,13 @@
         <v>18</v>
       </c>
       <c r="X15" t="s" s="2">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="Y15" t="s" s="2">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="Z15" t="s" s="2">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="AA15" t="s" s="2">
         <v>18</v>
@@ -3548,19 +3553,19 @@
         <v>18</v>
       </c>
       <c r="AF15" t="s" s="2">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="AG15" t="s" s="2">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="AH15" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AI15" t="s" s="2">
         <v>18</v>
       </c>
       <c r="AJ15" t="s" s="2">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="AK15" t="s" s="2">
         <v>18</v>
@@ -3572,10 +3577,10 @@
         <v>18</v>
       </c>
       <c r="AN15" t="s" s="2">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="AO15" t="s" s="2">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="AP15" t="s" s="2">
         <v>18</v>
@@ -3583,45 +3588,45 @@
     </row>
     <row r="16">
       <c r="A16" t="s" s="2">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="B16" t="s" s="2">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="C16" s="2"/>
       <c r="D16" t="s" s="2">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="E16" s="2"/>
       <c r="F16" t="s" s="2">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="G16" t="s" s="2">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="H16" t="s" s="2">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="I16" t="s" s="2">
         <v>18</v>
       </c>
       <c r="J16" t="s" s="2">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="K16" t="s" s="2">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="L16" t="s" s="2">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="M16" t="s" s="2">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="N16" t="s" s="2">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="O16" t="s" s="2">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="P16" t="s" s="2">
         <v>18</v>
@@ -3646,11 +3651,11 @@
         <v>18</v>
       </c>
       <c r="X16" t="s" s="2">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="Y16" s="2"/>
       <c r="Z16" t="s" s="2">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="AA16" t="s" s="2">
         <v>18</v>
@@ -3668,45 +3673,45 @@
         <v>18</v>
       </c>
       <c r="AF16" t="s" s="2">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="AG16" t="s" s="2">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="AH16" t="s" s="2">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="AI16" t="s" s="2">
         <v>18</v>
       </c>
       <c r="AJ16" t="s" s="2">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="AK16" t="s" s="2">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="AL16" t="s" s="2">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="AM16" t="s" s="2">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="AN16" t="s" s="2">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="AO16" t="s" s="2">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="AP16" t="s" s="2">
-        <v>211</v>
+        <v>212</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="s" s="2">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="B17" t="s" s="2">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="C17" s="2"/>
       <c r="D17" t="s" s="2">
@@ -3714,34 +3719,34 @@
       </c>
       <c r="E17" s="2"/>
       <c r="F17" t="s" s="2">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="G17" t="s" s="2">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="H17" t="s" s="2">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="I17" t="s" s="2">
         <v>18</v>
       </c>
       <c r="J17" t="s" s="2">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="K17" t="s" s="2">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="L17" t="s" s="2">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="M17" t="s" s="2">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="N17" t="s" s="2">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="O17" t="s" s="2">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="P17" t="s" s="2">
         <v>18</v>
@@ -3790,34 +3795,34 @@
         <v>18</v>
       </c>
       <c r="AF17" t="s" s="2">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="AG17" t="s" s="2">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="AH17" t="s" s="2">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="AI17" t="s" s="2">
         <v>18</v>
       </c>
       <c r="AJ17" t="s" s="2">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="AK17" t="s" s="2">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="AL17" t="s" s="2">
         <v>18</v>
       </c>
       <c r="AM17" t="s" s="2">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="AN17" t="s" s="2">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="AO17" t="s" s="2">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="AP17" t="s" s="2">
         <v>18</v>
@@ -3825,10 +3830,10 @@
     </row>
     <row r="18" hidden="true">
       <c r="A18" t="s" s="2">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="B18" t="s" s="2">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="C18" s="2"/>
       <c r="D18" t="s" s="2">
@@ -3836,10 +3841,10 @@
       </c>
       <c r="E18" s="2"/>
       <c r="F18" t="s" s="2">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="G18" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="H18" t="s" s="2">
         <v>18</v>
@@ -3848,19 +3853,19 @@
         <v>18</v>
       </c>
       <c r="J18" t="s" s="2">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="K18" t="s" s="2">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="L18" t="s" s="2">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="M18" t="s" s="2">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="N18" t="s" s="2">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="O18" s="2"/>
       <c r="P18" t="s" s="2">
@@ -3910,34 +3915,34 @@
         <v>18</v>
       </c>
       <c r="AF18" t="s" s="2">
+        <v>223</v>
+      </c>
+      <c r="AG18" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AH18" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AI18" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="AJ18" t="s" s="2">
+        <v>103</v>
+      </c>
+      <c r="AK18" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="AL18" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="AM18" t="s" s="2">
+        <v>209</v>
+      </c>
+      <c r="AN18" t="s" s="2">
+        <v>228</v>
+      </c>
+      <c r="AO18" t="s" s="2">
         <v>222</v>
-      </c>
-      <c r="AG18" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AH18" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AI18" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="AJ18" t="s" s="2">
-        <v>102</v>
-      </c>
-      <c r="AK18" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="AL18" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="AM18" t="s" s="2">
-        <v>208</v>
-      </c>
-      <c r="AN18" t="s" s="2">
-        <v>227</v>
-      </c>
-      <c r="AO18" t="s" s="2">
-        <v>221</v>
       </c>
       <c r="AP18" t="s" s="2">
         <v>18</v>
@@ -3945,21 +3950,21 @@
     </row>
     <row r="19" hidden="true">
       <c r="A19" t="s" s="2">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="B19" t="s" s="2">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="C19" s="2"/>
       <c r="D19" t="s" s="2">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="E19" s="2"/>
       <c r="F19" t="s" s="2">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="G19" t="s" s="2">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="H19" t="s" s="2">
         <v>18</v>
@@ -3968,22 +3973,22 @@
         <v>18</v>
       </c>
       <c r="J19" t="s" s="2">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="K19" t="s" s="2">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="L19" t="s" s="2">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="M19" t="s" s="2">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="N19" t="s" s="2">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="O19" t="s" s="2">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="P19" t="s" s="2">
         <v>18</v>
@@ -4032,34 +4037,34 @@
         <v>18</v>
       </c>
       <c r="AF19" t="s" s="2">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="AG19" t="s" s="2">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="AH19" t="s" s="2">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="AI19" t="s" s="2">
         <v>18</v>
       </c>
       <c r="AJ19" t="s" s="2">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="AK19" t="s" s="2">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="AL19" t="s" s="2">
         <v>18</v>
       </c>
       <c r="AM19" t="s" s="2">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="AN19" t="s" s="2">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="AO19" t="s" s="2">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="AP19" t="s" s="2">
         <v>18</v>
@@ -4067,45 +4072,45 @@
     </row>
     <row r="20">
       <c r="A20" t="s" s="2">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="B20" t="s" s="2">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="C20" s="2"/>
       <c r="D20" t="s" s="2">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="E20" s="2"/>
       <c r="F20" t="s" s="2">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="G20" t="s" s="2">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="H20" t="s" s="2">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="I20" t="s" s="2">
         <v>18</v>
       </c>
       <c r="J20" t="s" s="2">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="K20" t="s" s="2">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="L20" t="s" s="2">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="M20" t="s" s="2">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="N20" t="s" s="2">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="O20" t="s" s="2">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="P20" t="s" s="2">
         <v>18</v>
@@ -4154,34 +4159,34 @@
         <v>18</v>
       </c>
       <c r="AF20" t="s" s="2">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="AG20" t="s" s="2">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="AH20" t="s" s="2">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="AI20" t="s" s="2">
         <v>18</v>
       </c>
       <c r="AJ20" t="s" s="2">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="AK20" t="s" s="2">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="AL20" t="s" s="2">
         <v>18</v>
       </c>
       <c r="AM20" t="s" s="2">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="AN20" t="s" s="2">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="AO20" t="s" s="2">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="AP20" t="s" s="2">
         <v>18</v>
@@ -4189,10 +4194,10 @@
     </row>
     <row r="21" hidden="true">
       <c r="A21" t="s" s="2">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="B21" t="s" s="2">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="C21" s="2"/>
       <c r="D21" t="s" s="2">
@@ -4200,10 +4205,10 @@
       </c>
       <c r="E21" s="2"/>
       <c r="F21" t="s" s="2">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="G21" t="s" s="2">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="H21" t="s" s="2">
         <v>18</v>
@@ -4212,19 +4217,19 @@
         <v>18</v>
       </c>
       <c r="J21" t="s" s="2">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="K21" t="s" s="2">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="L21" t="s" s="2">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="M21" t="s" s="2">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="N21" t="s" s="2">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="O21" s="2"/>
       <c r="P21" t="s" s="2">
@@ -4274,19 +4279,19 @@
         <v>18</v>
       </c>
       <c r="AF21" t="s" s="2">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="AG21" t="s" s="2">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="AH21" t="s" s="2">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="AI21" t="s" s="2">
         <v>18</v>
       </c>
       <c r="AJ21" t="s" s="2">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="AK21" t="s" s="2">
         <v>18</v>
@@ -4295,13 +4300,13 @@
         <v>18</v>
       </c>
       <c r="AM21" t="s" s="2">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="AN21" t="s" s="2">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="AO21" t="s" s="2">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="AP21" t="s" s="2">
         <v>18</v>
@@ -4309,10 +4314,10 @@
     </row>
     <row r="22" hidden="true">
       <c r="A22" t="s" s="2">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="B22" t="s" s="2">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="C22" s="2"/>
       <c r="D22" t="s" s="2">
@@ -4320,10 +4325,10 @@
       </c>
       <c r="E22" s="2"/>
       <c r="F22" t="s" s="2">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="G22" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="H22" t="s" s="2">
         <v>18</v>
@@ -4332,20 +4337,20 @@
         <v>18</v>
       </c>
       <c r="J22" t="s" s="2">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="K22" t="s" s="2">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="L22" t="s" s="2">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="M22" t="s" s="2">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="N22" s="2"/>
       <c r="O22" t="s" s="2">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="P22" t="s" s="2">
         <v>18</v>
@@ -4394,34 +4399,34 @@
         <v>18</v>
       </c>
       <c r="AF22" t="s" s="2">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="AG22" t="s" s="2">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="AH22" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AI22" t="s" s="2">
         <v>18</v>
       </c>
       <c r="AJ22" t="s" s="2">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="AK22" t="s" s="2">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="AL22" t="s" s="2">
         <v>18</v>
       </c>
       <c r="AM22" t="s" s="2">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="AN22" t="s" s="2">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="AO22" t="s" s="2">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="AP22" t="s" s="2">
         <v>18</v>
@@ -4429,10 +4434,10 @@
     </row>
     <row r="23">
       <c r="A23" t="s" s="2">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="B23" t="s" s="2">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="C23" s="2"/>
       <c r="D23" t="s" s="2">
@@ -4440,34 +4445,34 @@
       </c>
       <c r="E23" s="2"/>
       <c r="F23" t="s" s="2">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="G23" t="s" s="2">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="H23" t="s" s="2">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="I23" t="s" s="2">
         <v>18</v>
       </c>
       <c r="J23" t="s" s="2">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="K23" t="s" s="2">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="L23" t="s" s="2">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="M23" t="s" s="2">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="N23" t="s" s="2">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="O23" t="s" s="2">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="P23" t="s" s="2">
         <v>18</v>
@@ -4516,45 +4521,45 @@
         <v>18</v>
       </c>
       <c r="AF23" t="s" s="2">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="AG23" t="s" s="2">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="AH23" t="s" s="2">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="AI23" t="s" s="2">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="AJ23" t="s" s="2">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="AK23" t="s" s="2">
         <v>18</v>
       </c>
       <c r="AL23" t="s" s="2">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="AM23" t="s" s="2">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="AN23" t="s" s="2">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="AO23" t="s" s="2">
         <v>18</v>
       </c>
       <c r="AP23" t="s" s="2">
-        <v>277</v>
+        <v>278</v>
       </c>
     </row>
     <row r="24" hidden="true">
       <c r="A24" t="s" s="2">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="B24" t="s" s="2">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="C24" s="2"/>
       <c r="D24" t="s" s="2">
@@ -4562,10 +4567,10 @@
       </c>
       <c r="E24" s="2"/>
       <c r="F24" t="s" s="2">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="G24" t="s" s="2">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="H24" t="s" s="2">
         <v>18</v>
@@ -4577,19 +4582,19 @@
         <v>18</v>
       </c>
       <c r="K24" t="s" s="2">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="L24" t="s" s="2">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="M24" t="s" s="2">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="N24" t="s" s="2">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="O24" t="s" s="2">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="P24" t="s" s="2">
         <v>18</v>
@@ -4614,13 +4619,13 @@
         <v>18</v>
       </c>
       <c r="X24" t="s" s="2">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="Y24" t="s" s="2">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="Z24" t="s" s="2">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="AA24" t="s" s="2">
         <v>18</v>
@@ -4638,19 +4643,19 @@
         <v>18</v>
       </c>
       <c r="AF24" t="s" s="2">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="AG24" t="s" s="2">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="AH24" t="s" s="2">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="AI24" t="s" s="2">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="AJ24" t="s" s="2">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="AK24" t="s" s="2">
         <v>18</v>
@@ -4659,10 +4664,10 @@
         <v>18</v>
       </c>
       <c r="AM24" t="s" s="2">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="AN24" t="s" s="2">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="AO24" t="s" s="2">
         <v>18</v>
@@ -4673,21 +4678,21 @@
     </row>
     <row r="25" hidden="true">
       <c r="A25" t="s" s="2">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="B25" t="s" s="2">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="C25" s="2"/>
       <c r="D25" t="s" s="2">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="E25" s="2"/>
       <c r="F25" t="s" s="2">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="G25" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="H25" t="s" s="2">
         <v>18</v>
@@ -4699,19 +4704,19 @@
         <v>18</v>
       </c>
       <c r="K25" t="s" s="2">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="L25" t="s" s="2">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="M25" t="s" s="2">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="N25" t="s" s="2">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="O25" t="s" s="2">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="P25" t="s" s="2">
         <v>18</v>
@@ -4736,13 +4741,13 @@
         <v>18</v>
       </c>
       <c r="X25" t="s" s="2">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="Y25" t="s" s="2">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="Z25" t="s" s="2">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="AA25" t="s" s="2">
         <v>18</v>
@@ -4760,45 +4765,45 @@
         <v>18</v>
       </c>
       <c r="AF25" t="s" s="2">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="AG25" t="s" s="2">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="AH25" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AI25" t="s" s="2">
         <v>18</v>
       </c>
       <c r="AJ25" t="s" s="2">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="AK25" t="s" s="2">
         <v>18</v>
       </c>
       <c r="AL25" t="s" s="2">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="AM25" t="s" s="2">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="AN25" t="s" s="2">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="AO25" t="s" s="2">
         <v>18</v>
       </c>
       <c r="AP25" t="s" s="2">
-        <v>298</v>
+        <v>299</v>
       </c>
     </row>
     <row r="26" hidden="true">
       <c r="A26" t="s" s="2">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="C26" s="2"/>
       <c r="D26" t="s" s="2">
@@ -4806,10 +4811,10 @@
       </c>
       <c r="E26" s="2"/>
       <c r="F26" t="s" s="2">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="G26" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="H26" t="s" s="2">
         <v>18</v>
@@ -4821,19 +4826,19 @@
         <v>18</v>
       </c>
       <c r="K26" t="s" s="2">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="L26" t="s" s="2">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="M26" t="s" s="2">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="N26" t="s" s="2">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="O26" t="s" s="2">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="P26" t="s" s="2">
         <v>18</v>
@@ -4882,19 +4887,19 @@
         <v>18</v>
       </c>
       <c r="AF26" t="s" s="2">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="AG26" t="s" s="2">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="AH26" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AI26" t="s" s="2">
         <v>18</v>
       </c>
       <c r="AJ26" t="s" s="2">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="AK26" t="s" s="2">
         <v>18</v>
@@ -4903,10 +4908,10 @@
         <v>18</v>
       </c>
       <c r="AM26" t="s" s="2">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="AN26" t="s" s="2">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="AO26" t="s" s="2">
         <v>18</v>
@@ -4917,10 +4922,10 @@
     </row>
     <row r="27" hidden="true">
       <c r="A27" t="s" s="2">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="C27" s="2"/>
       <c r="D27" t="s" s="2">
@@ -4928,10 +4933,10 @@
       </c>
       <c r="E27" s="2"/>
       <c r="F27" t="s" s="2">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="G27" t="s" s="2">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="H27" t="s" s="2">
         <v>18</v>
@@ -4943,16 +4948,16 @@
         <v>18</v>
       </c>
       <c r="K27" t="s" s="2">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="L27" t="s" s="2">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="M27" t="s" s="2">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="N27" t="s" s="2">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="O27" s="2"/>
       <c r="P27" t="s" s="2">
@@ -4978,13 +4983,13 @@
         <v>18</v>
       </c>
       <c r="X27" t="s" s="2">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="Y27" t="s" s="2">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="Z27" t="s" s="2">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="AA27" t="s" s="2">
         <v>18</v>
@@ -5002,45 +5007,45 @@
         <v>18</v>
       </c>
       <c r="AF27" t="s" s="2">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="AG27" t="s" s="2">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="AH27" t="s" s="2">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="AI27" t="s" s="2">
         <v>18</v>
       </c>
       <c r="AJ27" t="s" s="2">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="AK27" t="s" s="2">
         <v>18</v>
       </c>
       <c r="AL27" t="s" s="2">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="AM27" t="s" s="2">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="AN27" t="s" s="2">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="AO27" t="s" s="2">
         <v>18</v>
       </c>
       <c r="AP27" t="s" s="2">
-        <v>317</v>
+        <v>318</v>
       </c>
     </row>
     <row r="28" hidden="true">
       <c r="A28" t="s" s="2">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="B28" t="s" s="2">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="C28" s="2"/>
       <c r="D28" t="s" s="2">
@@ -5048,10 +5053,10 @@
       </c>
       <c r="E28" s="2"/>
       <c r="F28" t="s" s="2">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="G28" t="s" s="2">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="H28" t="s" s="2">
         <v>18</v>
@@ -5063,19 +5068,19 @@
         <v>18</v>
       </c>
       <c r="K28" t="s" s="2">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="L28" t="s" s="2">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="M28" t="s" s="2">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="N28" t="s" s="2">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="O28" t="s" s="2">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="P28" t="s" s="2">
         <v>18</v>
@@ -5100,13 +5105,13 @@
         <v>18</v>
       </c>
       <c r="X28" t="s" s="2">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="Y28" t="s" s="2">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="Z28" t="s" s="2">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="AA28" t="s" s="2">
         <v>18</v>
@@ -5124,19 +5129,19 @@
         <v>18</v>
       </c>
       <c r="AF28" t="s" s="2">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="AG28" t="s" s="2">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="AH28" t="s" s="2">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="AI28" t="s" s="2">
         <v>18</v>
       </c>
       <c r="AJ28" t="s" s="2">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="AK28" t="s" s="2">
         <v>18</v>
@@ -5145,10 +5150,10 @@
         <v>18</v>
       </c>
       <c r="AM28" t="s" s="2">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="AN28" t="s" s="2">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="AO28" t="s" s="2">
         <v>18</v>
@@ -5159,10 +5164,10 @@
     </row>
     <row r="29" hidden="true">
       <c r="A29" t="s" s="2">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="C29" s="2"/>
       <c r="D29" t="s" s="2">
@@ -5170,10 +5175,10 @@
       </c>
       <c r="E29" s="2"/>
       <c r="F29" t="s" s="2">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="G29" t="s" s="2">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="H29" t="s" s="2">
         <v>18</v>
@@ -5185,16 +5190,16 @@
         <v>18</v>
       </c>
       <c r="K29" t="s" s="2">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="L29" t="s" s="2">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="M29" t="s" s="2">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="N29" t="s" s="2">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="O29" s="2"/>
       <c r="P29" t="s" s="2">
@@ -5244,45 +5249,45 @@
         <v>18</v>
       </c>
       <c r="AF29" t="s" s="2">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="AG29" t="s" s="2">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="AH29" t="s" s="2">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="AI29" t="s" s="2">
         <v>18</v>
       </c>
       <c r="AJ29" t="s" s="2">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="AK29" t="s" s="2">
         <v>18</v>
       </c>
       <c r="AL29" t="s" s="2">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="AM29" t="s" s="2">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="AN29" t="s" s="2">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="AO29" t="s" s="2">
         <v>18</v>
       </c>
       <c r="AP29" t="s" s="2">
-        <v>335</v>
+        <v>336</v>
       </c>
     </row>
     <row r="30" hidden="true">
       <c r="A30" t="s" s="2">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="C30" s="2"/>
       <c r="D30" t="s" s="2">
@@ -5290,10 +5295,10 @@
       </c>
       <c r="E30" s="2"/>
       <c r="F30" t="s" s="2">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="G30" t="s" s="2">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="H30" t="s" s="2">
         <v>18</v>
@@ -5305,16 +5310,16 @@
         <v>18</v>
       </c>
       <c r="K30" t="s" s="2">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="L30" t="s" s="2">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="M30" t="s" s="2">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="N30" t="s" s="2">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="O30" s="2"/>
       <c r="P30" t="s" s="2">
@@ -5364,45 +5369,45 @@
         <v>18</v>
       </c>
       <c r="AF30" t="s" s="2">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="AG30" t="s" s="2">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="AH30" t="s" s="2">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="AI30" t="s" s="2">
         <v>18</v>
       </c>
       <c r="AJ30" t="s" s="2">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="AK30" t="s" s="2">
         <v>18</v>
       </c>
       <c r="AL30" t="s" s="2">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="AM30" t="s" s="2">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="AN30" t="s" s="2">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="AO30" t="s" s="2">
         <v>18</v>
       </c>
       <c r="AP30" t="s" s="2">
-        <v>344</v>
+        <v>345</v>
       </c>
     </row>
     <row r="31" hidden="true">
       <c r="A31" t="s" s="2">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="C31" s="2"/>
       <c r="D31" t="s" s="2">
@@ -5410,10 +5415,10 @@
       </c>
       <c r="E31" s="2"/>
       <c r="F31" t="s" s="2">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="G31" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="H31" t="s" s="2">
         <v>18</v>
@@ -5425,19 +5430,19 @@
         <v>18</v>
       </c>
       <c r="K31" t="s" s="2">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="L31" t="s" s="2">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="M31" t="s" s="2">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="N31" t="s" s="2">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="O31" t="s" s="2">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="P31" t="s" s="2">
         <v>18</v>
@@ -5486,19 +5491,19 @@
         <v>18</v>
       </c>
       <c r="AF31" t="s" s="2">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="AG31" t="s" s="2">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="AH31" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AI31" t="s" s="2">
         <v>18</v>
       </c>
       <c r="AJ31" t="s" s="2">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="AK31" t="s" s="2">
         <v>18</v>
@@ -5507,10 +5512,10 @@
         <v>18</v>
       </c>
       <c r="AM31" t="s" s="2">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="AN31" t="s" s="2">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="AO31" t="s" s="2">
         <v>18</v>
@@ -5521,10 +5526,10 @@
     </row>
     <row r="32" hidden="true">
       <c r="A32" t="s" s="2">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="C32" s="2"/>
       <c r="D32" t="s" s="2">
@@ -5532,10 +5537,10 @@
       </c>
       <c r="E32" s="2"/>
       <c r="F32" t="s" s="2">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="G32" t="s" s="2">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="H32" t="s" s="2">
         <v>18</v>
@@ -5547,13 +5552,13 @@
         <v>18</v>
       </c>
       <c r="K32" t="s" s="2">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="L32" t="s" s="2">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="M32" t="s" s="2">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="N32" s="2"/>
       <c r="O32" s="2"/>
@@ -5604,13 +5609,13 @@
         <v>18</v>
       </c>
       <c r="AF32" t="s" s="2">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="AG32" t="s" s="2">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="AH32" t="s" s="2">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="AI32" t="s" s="2">
         <v>18</v>
@@ -5628,7 +5633,7 @@
         <v>18</v>
       </c>
       <c r="AN32" t="s" s="2">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="AO32" t="s" s="2">
         <v>18</v>
@@ -5639,21 +5644,21 @@
     </row>
     <row r="33" hidden="true">
       <c r="A33" t="s" s="2">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="C33" s="2"/>
       <c r="D33" t="s" s="2">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="E33" s="2"/>
       <c r="F33" t="s" s="2">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="G33" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="H33" t="s" s="2">
         <v>18</v>
@@ -5665,16 +5670,16 @@
         <v>18</v>
       </c>
       <c r="K33" t="s" s="2">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="L33" t="s" s="2">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="M33" t="s" s="2">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="N33" t="s" s="2">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="O33" s="2"/>
       <c r="P33" t="s" s="2">
@@ -5724,19 +5729,19 @@
         <v>18</v>
       </c>
       <c r="AF33" t="s" s="2">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="AG33" t="s" s="2">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="AH33" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AI33" t="s" s="2">
         <v>18</v>
       </c>
       <c r="AJ33" t="s" s="2">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="AK33" t="s" s="2">
         <v>18</v>
@@ -5748,7 +5753,7 @@
         <v>18</v>
       </c>
       <c r="AN33" t="s" s="2">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="AO33" t="s" s="2">
         <v>18</v>
@@ -5759,45 +5764,45 @@
     </row>
     <row r="34" hidden="true">
       <c r="A34" t="s" s="2">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="C34" s="2"/>
       <c r="D34" t="s" s="2">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="E34" s="2"/>
       <c r="F34" t="s" s="2">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="G34" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="H34" t="s" s="2">
         <v>18</v>
       </c>
       <c r="I34" t="s" s="2">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="J34" t="s" s="2">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="K34" t="s" s="2">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="L34" t="s" s="2">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="M34" t="s" s="2">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="N34" t="s" s="2">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="O34" t="s" s="2">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="P34" t="s" s="2">
         <v>18</v>
@@ -5846,19 +5851,19 @@
         <v>18</v>
       </c>
       <c r="AF34" t="s" s="2">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="AG34" t="s" s="2">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="AH34" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AI34" t="s" s="2">
         <v>18</v>
       </c>
       <c r="AJ34" t="s" s="2">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="AK34" t="s" s="2">
         <v>18</v>
@@ -5870,7 +5875,7 @@
         <v>18</v>
       </c>
       <c r="AN34" t="s" s="2">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="AO34" t="s" s="2">
         <v>18</v>
@@ -5881,10 +5886,10 @@
     </row>
     <row r="35" hidden="true">
       <c r="A35" t="s" s="2">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
@@ -5892,10 +5897,10 @@
       </c>
       <c r="E35" s="2"/>
       <c r="F35" t="s" s="2">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="G35" t="s" s="2">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="H35" t="s" s="2">
         <v>18</v>
@@ -5907,13 +5912,13 @@
         <v>18</v>
       </c>
       <c r="K35" t="s" s="2">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="L35" t="s" s="2">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="M35" t="s" s="2">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="N35" s="2"/>
       <c r="O35" s="2"/>
@@ -5964,19 +5969,19 @@
         <v>18</v>
       </c>
       <c r="AF35" t="s" s="2">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="AG35" t="s" s="2">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="AH35" t="s" s="2">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="AI35" t="s" s="2">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="AJ35" t="s" s="2">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="AK35" t="s" s="2">
         <v>18</v>
@@ -5985,10 +5990,10 @@
         <v>18</v>
       </c>
       <c r="AM35" t="s" s="2">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="AN35" t="s" s="2">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="AO35" t="s" s="2">
         <v>18</v>
@@ -5999,10 +6004,10 @@
     </row>
     <row r="36" hidden="true">
       <c r="A36" t="s" s="2">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
@@ -6010,10 +6015,10 @@
       </c>
       <c r="E36" s="2"/>
       <c r="F36" t="s" s="2">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="G36" t="s" s="2">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="H36" t="s" s="2">
         <v>18</v>
@@ -6025,13 +6030,13 @@
         <v>18</v>
       </c>
       <c r="K36" t="s" s="2">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="L36" t="s" s="2">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="M36" t="s" s="2">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="N36" s="2"/>
       <c r="O36" s="2"/>
@@ -6082,19 +6087,19 @@
         <v>18</v>
       </c>
       <c r="AF36" t="s" s="2">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="AG36" t="s" s="2">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="AH36" t="s" s="2">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="AI36" t="s" s="2">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="AJ36" t="s" s="2">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="AK36" t="s" s="2">
         <v>18</v>
@@ -6103,10 +6108,10 @@
         <v>18</v>
       </c>
       <c r="AM36" t="s" s="2">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="AN36" t="s" s="2">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="AO36" t="s" s="2">
         <v>18</v>
@@ -6117,10 +6122,10 @@
     </row>
     <row r="37" hidden="true">
       <c r="A37" t="s" s="2">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
@@ -6128,10 +6133,10 @@
       </c>
       <c r="E37" s="2"/>
       <c r="F37" t="s" s="2">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="G37" t="s" s="2">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="H37" t="s" s="2">
         <v>18</v>
@@ -6143,19 +6148,19 @@
         <v>18</v>
       </c>
       <c r="K37" t="s" s="2">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="L37" t="s" s="2">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="M37" t="s" s="2">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="N37" t="s" s="2">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="O37" t="s" s="2">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="P37" t="s" s="2">
         <v>18</v>
@@ -6180,13 +6185,13 @@
         <v>18</v>
       </c>
       <c r="X37" t="s" s="2">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="Y37" t="s" s="2">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="Z37" t="s" s="2">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="AA37" t="s" s="2">
         <v>18</v>
@@ -6204,31 +6209,31 @@
         <v>18</v>
       </c>
       <c r="AF37" t="s" s="2">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="AG37" t="s" s="2">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="AH37" t="s" s="2">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="AI37" t="s" s="2">
         <v>18</v>
       </c>
       <c r="AJ37" t="s" s="2">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="AK37" t="s" s="2">
         <v>18</v>
       </c>
       <c r="AL37" t="s" s="2">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="AM37" t="s" s="2">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="AN37" t="s" s="2">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="AO37" t="s" s="2">
         <v>18</v>
@@ -6239,10 +6244,10 @@
     </row>
     <row r="38" hidden="true">
       <c r="A38" t="s" s="2">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
@@ -6250,10 +6255,10 @@
       </c>
       <c r="E38" s="2"/>
       <c r="F38" t="s" s="2">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="G38" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="H38" t="s" s="2">
         <v>18</v>
@@ -6265,19 +6270,19 @@
         <v>18</v>
       </c>
       <c r="K38" t="s" s="2">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="L38" t="s" s="2">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="M38" t="s" s="2">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="N38" t="s" s="2">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="O38" t="s" s="2">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="P38" t="s" s="2">
         <v>18</v>
@@ -6302,13 +6307,13 @@
         <v>18</v>
       </c>
       <c r="X38" t="s" s="2">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="Y38" t="s" s="2">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="Z38" t="s" s="2">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="AA38" t="s" s="2">
         <v>18</v>
@@ -6326,31 +6331,31 @@
         <v>18</v>
       </c>
       <c r="AF38" t="s" s="2">
+        <v>389</v>
+      </c>
+      <c r="AG38" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AH38" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AI38" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="AJ38" t="s" s="2">
+        <v>103</v>
+      </c>
+      <c r="AK38" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="AL38" t="s" s="2">
+        <v>387</v>
+      </c>
+      <c r="AM38" t="s" s="2">
         <v>388</v>
       </c>
-      <c r="AG38" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AH38" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AI38" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="AJ38" t="s" s="2">
-        <v>102</v>
-      </c>
-      <c r="AK38" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="AL38" t="s" s="2">
-        <v>386</v>
-      </c>
-      <c r="AM38" t="s" s="2">
-        <v>387</v>
-      </c>
       <c r="AN38" t="s" s="2">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="AO38" t="s" s="2">
         <v>18</v>
@@ -6361,10 +6366,10 @@
     </row>
     <row r="39" hidden="true">
       <c r="A39" t="s" s="2">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
@@ -6372,10 +6377,10 @@
       </c>
       <c r="E39" s="2"/>
       <c r="F39" t="s" s="2">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="G39" t="s" s="2">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="H39" t="s" s="2">
         <v>18</v>
@@ -6387,17 +6392,17 @@
         <v>18</v>
       </c>
       <c r="K39" t="s" s="2">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="L39" t="s" s="2">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="M39" t="s" s="2">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="N39" s="2"/>
       <c r="O39" t="s" s="2">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="P39" t="s" s="2">
         <v>18</v>
@@ -6446,19 +6451,19 @@
         <v>18</v>
       </c>
       <c r="AF39" t="s" s="2">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="AG39" t="s" s="2">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="AH39" t="s" s="2">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="AI39" t="s" s="2">
         <v>18</v>
       </c>
       <c r="AJ39" t="s" s="2">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="AK39" t="s" s="2">
         <v>18</v>
@@ -6470,7 +6475,7 @@
         <v>18</v>
       </c>
       <c r="AN39" t="s" s="2">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="AO39" t="s" s="2">
         <v>18</v>
@@ -6481,10 +6486,10 @@
     </row>
     <row r="40" hidden="true">
       <c r="A40" t="s" s="2">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
@@ -6492,10 +6497,10 @@
       </c>
       <c r="E40" s="2"/>
       <c r="F40" t="s" s="2">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="G40" t="s" s="2">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="H40" t="s" s="2">
         <v>18</v>
@@ -6507,13 +6512,13 @@
         <v>18</v>
       </c>
       <c r="K40" t="s" s="2">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="L40" t="s" s="2">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="M40" t="s" s="2">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="N40" s="2"/>
       <c r="O40" s="2"/>
@@ -6564,19 +6569,19 @@
         <v>18</v>
       </c>
       <c r="AF40" t="s" s="2">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="AG40" t="s" s="2">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="AH40" t="s" s="2">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="AI40" t="s" s="2">
         <v>18</v>
       </c>
       <c r="AJ40" t="s" s="2">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="AK40" t="s" s="2">
         <v>18</v>
@@ -6585,10 +6590,10 @@
         <v>18</v>
       </c>
       <c r="AM40" t="s" s="2">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="AN40" t="s" s="2">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="AO40" t="s" s="2">
         <v>18</v>
@@ -6599,10 +6604,10 @@
     </row>
     <row r="41" hidden="true">
       <c r="A41" t="s" s="2">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
@@ -6610,10 +6615,10 @@
       </c>
       <c r="E41" s="2"/>
       <c r="F41" t="s" s="2">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="G41" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="H41" t="s" s="2">
         <v>18</v>
@@ -6622,19 +6627,19 @@
         <v>18</v>
       </c>
       <c r="J41" t="s" s="2">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="K41" t="s" s="2">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="L41" t="s" s="2">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="M41" t="s" s="2">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="N41" t="s" s="2">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="O41" s="2"/>
       <c r="P41" t="s" s="2">
@@ -6684,19 +6689,19 @@
         <v>18</v>
       </c>
       <c r="AF41" t="s" s="2">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="AG41" t="s" s="2">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="AH41" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AI41" t="s" s="2">
         <v>18</v>
       </c>
       <c r="AJ41" t="s" s="2">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="AK41" t="s" s="2">
         <v>18</v>
@@ -6705,10 +6710,10 @@
         <v>18</v>
       </c>
       <c r="AM41" t="s" s="2">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="AN41" t="s" s="2">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="AO41" t="s" s="2">
         <v>18</v>
@@ -6719,10 +6724,10 @@
     </row>
     <row r="42" hidden="true">
       <c r="A42" t="s" s="2">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
@@ -6730,10 +6735,10 @@
       </c>
       <c r="E42" s="2"/>
       <c r="F42" t="s" s="2">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="G42" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="H42" t="s" s="2">
         <v>18</v>
@@ -6742,19 +6747,19 @@
         <v>18</v>
       </c>
       <c r="J42" t="s" s="2">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="K42" t="s" s="2">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="L42" t="s" s="2">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="M42" t="s" s="2">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="N42" t="s" s="2">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="O42" s="2"/>
       <c r="P42" t="s" s="2">
@@ -6804,19 +6809,19 @@
         <v>18</v>
       </c>
       <c r="AF42" t="s" s="2">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="AG42" t="s" s="2">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="AH42" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AI42" t="s" s="2">
         <v>18</v>
       </c>
       <c r="AJ42" t="s" s="2">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="AK42" t="s" s="2">
         <v>18</v>
@@ -6825,10 +6830,10 @@
         <v>18</v>
       </c>
       <c r="AM42" t="s" s="2">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="AN42" t="s" s="2">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="AO42" t="s" s="2">
         <v>18</v>
@@ -6839,10 +6844,10 @@
     </row>
     <row r="43" hidden="true">
       <c r="A43" t="s" s="2">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
@@ -6850,10 +6855,10 @@
       </c>
       <c r="E43" s="2"/>
       <c r="F43" t="s" s="2">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="G43" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="H43" t="s" s="2">
         <v>18</v>
@@ -6862,22 +6867,22 @@
         <v>18</v>
       </c>
       <c r="J43" t="s" s="2">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="K43" t="s" s="2">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="L43" t="s" s="2">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="M43" t="s" s="2">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="N43" t="s" s="2">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="O43" t="s" s="2">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="P43" t="s" s="2">
         <v>18</v>
@@ -6926,19 +6931,19 @@
         <v>18</v>
       </c>
       <c r="AF43" t="s" s="2">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="AG43" t="s" s="2">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="AH43" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AI43" t="s" s="2">
         <v>18</v>
       </c>
       <c r="AJ43" t="s" s="2">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="AK43" t="s" s="2">
         <v>18</v>
@@ -6947,10 +6952,10 @@
         <v>18</v>
       </c>
       <c r="AM43" t="s" s="2">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="AN43" t="s" s="2">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="AO43" t="s" s="2">
         <v>18</v>
@@ -6961,10 +6966,10 @@
     </row>
     <row r="44" hidden="true">
       <c r="A44" t="s" s="2">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
@@ -6972,10 +6977,10 @@
       </c>
       <c r="E44" s="2"/>
       <c r="F44" t="s" s="2">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="G44" t="s" s="2">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="H44" t="s" s="2">
         <v>18</v>
@@ -6987,13 +6992,13 @@
         <v>18</v>
       </c>
       <c r="K44" t="s" s="2">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="L44" t="s" s="2">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="M44" t="s" s="2">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="N44" s="2"/>
       <c r="O44" s="2"/>
@@ -7044,13 +7049,13 @@
         <v>18</v>
       </c>
       <c r="AF44" t="s" s="2">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="AG44" t="s" s="2">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="AH44" t="s" s="2">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="AI44" t="s" s="2">
         <v>18</v>
@@ -7068,7 +7073,7 @@
         <v>18</v>
       </c>
       <c r="AN44" t="s" s="2">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="AO44" t="s" s="2">
         <v>18</v>
@@ -7079,21 +7084,21 @@
     </row>
     <row r="45" hidden="true">
       <c r="A45" t="s" s="2">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="E45" s="2"/>
       <c r="F45" t="s" s="2">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="G45" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="H45" t="s" s="2">
         <v>18</v>
@@ -7105,16 +7110,16 @@
         <v>18</v>
       </c>
       <c r="K45" t="s" s="2">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="L45" t="s" s="2">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="M45" t="s" s="2">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="N45" t="s" s="2">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="O45" s="2"/>
       <c r="P45" t="s" s="2">
@@ -7164,19 +7169,19 @@
         <v>18</v>
       </c>
       <c r="AF45" t="s" s="2">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="AG45" t="s" s="2">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="AH45" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AI45" t="s" s="2">
         <v>18</v>
       </c>
       <c r="AJ45" t="s" s="2">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="AK45" t="s" s="2">
         <v>18</v>
@@ -7188,7 +7193,7 @@
         <v>18</v>
       </c>
       <c r="AN45" t="s" s="2">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="AO45" t="s" s="2">
         <v>18</v>
@@ -7199,45 +7204,45 @@
     </row>
     <row r="46" hidden="true">
       <c r="A46" t="s" s="2">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="E46" s="2"/>
       <c r="F46" t="s" s="2">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="G46" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="H46" t="s" s="2">
         <v>18</v>
       </c>
       <c r="I46" t="s" s="2">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="J46" t="s" s="2">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="K46" t="s" s="2">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="L46" t="s" s="2">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="M46" t="s" s="2">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="N46" t="s" s="2">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="O46" t="s" s="2">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="P46" t="s" s="2">
         <v>18</v>
@@ -7286,19 +7291,19 @@
         <v>18</v>
       </c>
       <c r="AF46" t="s" s="2">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="AG46" t="s" s="2">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="AH46" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AI46" t="s" s="2">
         <v>18</v>
       </c>
       <c r="AJ46" t="s" s="2">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="AK46" t="s" s="2">
         <v>18</v>
@@ -7310,7 +7315,7 @@
         <v>18</v>
       </c>
       <c r="AN46" t="s" s="2">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="AO46" t="s" s="2">
         <v>18</v>
@@ -7321,10 +7326,10 @@
     </row>
     <row r="47" hidden="true">
       <c r="A47" t="s" s="2">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
@@ -7332,10 +7337,10 @@
       </c>
       <c r="E47" s="2"/>
       <c r="F47" t="s" s="2">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="G47" t="s" s="2">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="H47" t="s" s="2">
         <v>18</v>
@@ -7344,22 +7349,22 @@
         <v>18</v>
       </c>
       <c r="J47" t="s" s="2">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="K47" t="s" s="2">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="L47" t="s" s="2">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="M47" t="s" s="2">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="N47" t="s" s="2">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="O47" t="s" s="2">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="P47" t="s" s="2">
         <v>18</v>
@@ -7384,13 +7389,13 @@
         <v>18</v>
       </c>
       <c r="X47" t="s" s="2">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="Y47" t="s" s="2">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="Z47" t="s" s="2">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="AA47" t="s" s="2">
         <v>18</v>
@@ -7408,34 +7413,34 @@
         <v>18</v>
       </c>
       <c r="AF47" t="s" s="2">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="AG47" t="s" s="2">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="AH47" t="s" s="2">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="AI47" t="s" s="2">
         <v>18</v>
       </c>
       <c r="AJ47" t="s" s="2">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="AK47" t="s" s="2">
         <v>18</v>
       </c>
       <c r="AL47" t="s" s="2">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="AM47" t="s" s="2">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="AN47" t="s" s="2">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="AO47" t="s" s="2">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="AP47" t="s" s="2">
         <v>18</v>
@@ -7443,10 +7448,10 @@
     </row>
     <row r="48" hidden="true">
       <c r="A48" t="s" s="2">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
@@ -7454,10 +7459,10 @@
       </c>
       <c r="E48" s="2"/>
       <c r="F48" t="s" s="2">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="G48" t="s" s="2">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="H48" t="s" s="2">
         <v>18</v>
@@ -7466,22 +7471,22 @@
         <v>18</v>
       </c>
       <c r="J48" t="s" s="2">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="K48" t="s" s="2">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="L48" t="s" s="2">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="M48" t="s" s="2">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="N48" t="s" s="2">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="O48" t="s" s="2">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="P48" t="s" s="2">
         <v>18</v>
@@ -7530,45 +7535,45 @@
         <v>18</v>
       </c>
       <c r="AF48" t="s" s="2">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="AG48" t="s" s="2">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="AH48" t="s" s="2">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="AI48" t="s" s="2">
         <v>18</v>
       </c>
       <c r="AJ48" t="s" s="2">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="AK48" t="s" s="2">
         <v>18</v>
       </c>
       <c r="AL48" t="s" s="2">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="AM48" t="s" s="2">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="AN48" t="s" s="2">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="AO48" t="s" s="2">
         <v>18</v>
       </c>
       <c r="AP48" t="s" s="2">
-        <v>277</v>
+        <v>278</v>
       </c>
     </row>
     <row r="49" hidden="true">
       <c r="A49" t="s" s="2">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
@@ -7576,10 +7581,10 @@
       </c>
       <c r="E49" s="2"/>
       <c r="F49" t="s" s="2">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="G49" t="s" s="2">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="H49" t="s" s="2">
         <v>18</v>
@@ -7591,19 +7596,19 @@
         <v>18</v>
       </c>
       <c r="K49" t="s" s="2">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="L49" t="s" s="2">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="M49" t="s" s="2">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="N49" t="s" s="2">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="O49" t="s" s="2">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="P49" t="s" s="2">
         <v>18</v>
@@ -7628,13 +7633,13 @@
         <v>18</v>
       </c>
       <c r="X49" t="s" s="2">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="Y49" t="s" s="2">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="Z49" t="s" s="2">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="AA49" t="s" s="2">
         <v>18</v>
@@ -7652,19 +7657,19 @@
         <v>18</v>
       </c>
       <c r="AF49" t="s" s="2">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="AG49" t="s" s="2">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="AH49" t="s" s="2">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="AI49" t="s" s="2">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="AJ49" t="s" s="2">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="AK49" t="s" s="2">
         <v>18</v>
@@ -7673,10 +7678,10 @@
         <v>18</v>
       </c>
       <c r="AM49" t="s" s="2">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="AN49" t="s" s="2">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="AO49" t="s" s="2">
         <v>18</v>
@@ -7687,21 +7692,21 @@
     </row>
     <row r="50" hidden="true">
       <c r="A50" t="s" s="2">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="E50" s="2"/>
       <c r="F50" t="s" s="2">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="G50" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="H50" t="s" s="2">
         <v>18</v>
@@ -7713,19 +7718,19 @@
         <v>18</v>
       </c>
       <c r="K50" t="s" s="2">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="L50" t="s" s="2">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="M50" t="s" s="2">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="N50" t="s" s="2">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="O50" t="s" s="2">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="P50" t="s" s="2">
         <v>18</v>
@@ -7750,13 +7755,13 @@
         <v>18</v>
       </c>
       <c r="X50" t="s" s="2">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="Y50" t="s" s="2">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="Z50" t="s" s="2">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="AA50" t="s" s="2">
         <v>18</v>
@@ -7774,45 +7779,45 @@
         <v>18</v>
       </c>
       <c r="AF50" t="s" s="2">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="AG50" t="s" s="2">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="AH50" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AI50" t="s" s="2">
         <v>18</v>
       </c>
       <c r="AJ50" t="s" s="2">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="AK50" t="s" s="2">
         <v>18</v>
       </c>
       <c r="AL50" t="s" s="2">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="AM50" t="s" s="2">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="AN50" t="s" s="2">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="AO50" t="s" s="2">
         <v>18</v>
       </c>
       <c r="AP50" t="s" s="2">
-        <v>298</v>
+        <v>299</v>
       </c>
     </row>
     <row r="51" hidden="true">
       <c r="A51" t="s" s="2">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
@@ -7820,10 +7825,10 @@
       </c>
       <c r="E51" s="2"/>
       <c r="F51" t="s" s="2">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="G51" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="H51" t="s" s="2">
         <v>18</v>
@@ -7835,19 +7840,19 @@
         <v>18</v>
       </c>
       <c r="K51" t="s" s="2">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="L51" t="s" s="2">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="M51" t="s" s="2">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="N51" t="s" s="2">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="O51" t="s" s="2">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="P51" t="s" s="2">
         <v>18</v>
@@ -7896,19 +7901,19 @@
         <v>18</v>
       </c>
       <c r="AF51" t="s" s="2">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="AG51" t="s" s="2">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="AH51" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AI51" t="s" s="2">
         <v>18</v>
       </c>
       <c r="AJ51" t="s" s="2">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="AK51" t="s" s="2">
         <v>18</v>
@@ -7917,10 +7922,10 @@
         <v>18</v>
       </c>
       <c r="AM51" t="s" s="2">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="AN51" t="s" s="2">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="AO51" t="s" s="2">
         <v>18</v>

--- a/StructureDefinition-swallowing-screening-result.xlsx
+++ b/StructureDefinition-swallowing-screening-result.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.1.0</t>
+    <t>1.1.1</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-29T08:35:16+00:00</t>
+    <t>2026-07-29T12:05:46+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -87,7 +87,7 @@
     <t>Copyright</t>
   </si>
   <si>
-    <t>© 2026 N. Kapan Tunçer and S. Tunçer. IG artifacts licensed under the MIT License. This IG references but does not redistribute SNOMED CT (© SNOMED International), LOINC (© Regenstrief Institute, Inc.) and the IDDSI framework (CC BY-SA 4.0, used unmodified); value sets enumerate concept identifiers only, so display terms are supplied at expansion time by the implementer's own terminology server. Implementers are responsible for holding the applicable third-party licences.</t>
+    <t>© 2026 N. Kapan Tunçer and S. Tunçer. IG artifacts licensed under the MIT License. This IG carries concept identifiers from SNOMED CT (© SNOMED International), LOINC (© Regenstrief Institute, Inc.) and the IDDSI framework (CC BY-SA 4.0, used unmodified); it redistributes no code system release, national extension or semantic content. Value sets enumerate identifiers, and some members additionally carry the English term as an unmodified display hint; the authoritative display is supplied at expansion time by the implementer's own terminology server. Implementers are responsible for holding the applicable third-party licences.</t>
   </si>
   <si>
     <t>FHIR Version</t>

--- a/StructureDefinition-swallowing-screening-result.xlsx
+++ b/StructureDefinition-swallowing-screening-result.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.1.1</t>
+    <t>1.2.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-29T12:05:46+00:00</t>
+    <t>2026-07-31T09:21:13+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-swallowing-screening-result.xlsx
+++ b/StructureDefinition-swallowing-screening-result.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.2.0</t>
+    <t>1.2.1</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-31T09:21:13+00:00</t>
+    <t>2026-08-13T14:00:50+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -87,7 +87,7 @@
     <t>Copyright</t>
   </si>
   <si>
-    <t>© 2026 N. Kapan Tunçer and S. Tunçer. IG artifacts licensed under the MIT License. This IG carries concept identifiers from SNOMED CT (© SNOMED International), LOINC (© Regenstrief Institute, Inc.) and the IDDSI framework (CC BY-SA 4.0, used unmodified); it redistributes no code system release, national extension or semantic content. Value sets enumerate identifiers, and some members additionally carry the English term as an unmodified display hint; the authoritative display is supplied at expansion time by the implementer's own terminology server. Implementers are responsible for holding the applicable third-party licences.</t>
+    <t>Profile definition: MIT (© 2026 N. Kapan Tunçer and S. Tunçer). This profile carries third-party concept identifiers rather than the terminologies themselves. SNOMED CT® is a registered trademark of SNOMED International; concept identifiers and English terms are © SNOMED International, used under the Global Patient Set licence (CC BY-ND 4.0) and reproduced verbatim, with none translated, shortened or otherwise altered. Implementers remain responsible for holding the applicable third-party licences in their own territory.</t>
   </si>
   <si>
     <t>FHIR Version</t>

--- a/StructureDefinition-swallowing-screening-result.xlsx
+++ b/StructureDefinition-swallowing-screening-result.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.2.1</t>
+    <t>1.2.2</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-13T14:00:50+00:00</t>
+    <t>2026-08-13T23:31:20+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -87,7 +87,7 @@
     <t>Copyright</t>
   </si>
   <si>
-    <t>Profile definition: MIT (© 2026 N. Kapan Tunçer and S. Tunçer). This profile carries third-party concept identifiers rather than the terminologies themselves. SNOMED CT® is a registered trademark of SNOMED International; concept identifiers and English terms are © SNOMED International, used under the Global Patient Set licence (CC BY-ND 4.0) and reproduced verbatim, with none translated, shortened or otherwise altered. Implementers remain responsible for holding the applicable third-party licences in their own territory.</t>
+    <t>Profile definition: MIT (© 2026 N. Kapan Tunçer and S. Tunçer). This profile carries third-party concept identifiers rather than the terminologies themselves. SNOMED CT® is a registered trademark of SNOMED International; concept identifiers and English terms are © SNOMED International, used under the Global Patient Set licence (CC BY-ND 4.0, https://creativecommons.org/licenses/by-nd/4.0/) and reproduced verbatim, with none translated, shortened or otherwise altered. Implementers remain responsible for holding the applicable third-party licences in their own territory.</t>
   </si>
   <si>
     <t>FHIR Version</t>

--- a/StructureDefinition-swallowing-screening-result.xlsx
+++ b/StructureDefinition-swallowing-screening-result.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.2.2</t>
+    <t>1.2.3</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-13T23:31:20+00:00</t>
+    <t>2026-08-14T00:08:39+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-swallowing-screening-result.xlsx
+++ b/StructureDefinition-swallowing-screening-result.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.2.3</t>
+    <t>1.2.4</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-14T00:08:39+00:00</t>
+    <t>2026-08-14T00:48:45+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-swallowing-screening-result.xlsx
+++ b/StructureDefinition-swallowing-screening-result.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.2.4</t>
+    <t>1.2.5</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-14T00:48:45+00:00</t>
+    <t>2026-08-15T14:40:00+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-swallowing-screening-result.xlsx
+++ b/StructureDefinition-swallowing-screening-result.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.2.5</t>
+    <t>1.3.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-15T14:40:00+00:00</t>
+    <t>2026-08-18T10:55:39+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-swallowing-screening-result.xlsx
+++ b/StructureDefinition-swallowing-screening-result.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.3.0</t>
+    <t>1.3.1</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-18T10:55:39+00:00</t>
+    <t>2026-08-18T13:05:08+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-swallowing-screening-result.xlsx
+++ b/StructureDefinition-swallowing-screening-result.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.3.1</t>
+    <t>1.3.2</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-18T13:05:08+00:00</t>
+    <t>2026-08-18T14:23:53+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-swallowing-screening-result.xlsx
+++ b/StructureDefinition-swallowing-screening-result.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.3.2</t>
+    <t>1.3.3</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-18T14:23:53+00:00</t>
+    <t>2026-08-19T10:42:48+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
